--- a/sample-data/TA_requisitions_2026-05.xlsx
+++ b/sample-data/TA_requisitions_2026-05.xlsx
@@ -466,61 +466,61 @@
         <v>REQ-2026-01</v>
       </c>
       <c r="B2" t="str">
-        <v>Sales</v>
+        <v>Finance</v>
       </c>
       <c r="C2" t="str">
-        <v>SMB</v>
+        <v>Accounts</v>
       </c>
       <c r="D2" t="str">
-        <v>Regional Manager</v>
+        <v>Finance Analyst</v>
       </c>
       <c r="E2" t="str">
-        <v>L3</v>
+        <v>L5</v>
       </c>
       <c r="F2" t="str">
-        <v>Remote</v>
+        <v>Pune</v>
       </c>
       <c r="G2" t="str">
-        <v>Sara Shah</v>
+        <v>Priya Sheikh</v>
       </c>
       <c r="H2" t="str">
-        <v>Intern</v>
+        <v>FT</v>
       </c>
       <c r="I2" t="str">
-        <v>On-hold</v>
+        <v>Open</v>
       </c>
       <c r="J2" t="str">
-        <v>2025-11-26</v>
+        <v>2025-08-17</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-08-07</v>
+        <v>2026-07-16</v>
       </c>
       <c r="L2">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="M2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O2">
+        <v>8</v>
+      </c>
+      <c r="P2">
         <v>7</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>6</v>
       </c>
-      <c r="Q2">
-        <v>5</v>
-      </c>
       <c r="R2" t="str">
-        <v>Agency</v>
+        <v>Internal</v>
       </c>
       <c r="S2" t="str">
-        <v>Vikram Bhat</v>
+        <v>Nisha Mehta</v>
       </c>
       <c r="T2">
-        <v>43239</v>
+        <v>103731</v>
       </c>
     </row>
     <row r="3">
@@ -528,61 +528,61 @@
         <v>REQ-2026-02</v>
       </c>
       <c r="B3" t="str">
-        <v>Customer Support</v>
+        <v>Product</v>
       </c>
       <c r="C3" t="str">
-        <v>L1 Support</v>
+        <v>Core Product</v>
       </c>
       <c r="D3" t="str">
-        <v>Support Lead</v>
+        <v>Associate PM</v>
       </c>
       <c r="E3" t="str">
-        <v>L6</v>
+        <v>L5</v>
       </c>
       <c r="F3" t="str">
-        <v>Mumbai</v>
+        <v>Remote</v>
       </c>
       <c r="G3" t="str">
-        <v>Karan Lopes</v>
+        <v>Anjali Khan</v>
       </c>
       <c r="H3" t="str">
-        <v>Contract</v>
+        <v>Intern</v>
       </c>
       <c r="I3" t="str">
-        <v>Filled</v>
+        <v>Open</v>
       </c>
       <c r="J3" t="str">
-        <v>2025-10-27</v>
+        <v>2025-11-21</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-08-02</v>
+        <v>2026-06-03</v>
       </c>
       <c r="L3">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="N3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R3" t="str">
-        <v>Internal</v>
+        <v>Agency</v>
       </c>
       <c r="S3" t="str">
-        <v>Myra Gupta</v>
+        <v>Sai Singh</v>
       </c>
       <c r="T3">
-        <v>93362</v>
+        <v>47098</v>
       </c>
     </row>
     <row r="4">
@@ -590,61 +590,61 @@
         <v>REQ-2026-03</v>
       </c>
       <c r="B4" t="str">
-        <v>Marketing</v>
+        <v>Customer Support</v>
       </c>
       <c r="C4" t="str">
-        <v>Digital</v>
+        <v>L1 Support</v>
       </c>
       <c r="D4" t="str">
-        <v>Marketing Executive</v>
+        <v>Support Associate</v>
       </c>
       <c r="E4" t="str">
-        <v>L3</v>
+        <v>L5</v>
       </c>
       <c r="F4" t="str">
-        <v>Bengaluru</v>
+        <v>Mumbai</v>
       </c>
       <c r="G4" t="str">
-        <v>Zoya Desai</v>
+        <v>Nikhil Banerjee</v>
       </c>
       <c r="H4" t="str">
-        <v>Contract</v>
+        <v>FT</v>
       </c>
       <c r="I4" t="str">
         <v>Filled</v>
       </c>
       <c r="J4" t="str">
-        <v>2025-09-21</v>
+        <v>2025-11-18</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-05-08</v>
+        <v>2026-07-27</v>
       </c>
       <c r="L4">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="M4">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="N4">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="O4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R4" t="str">
         <v>Direct</v>
       </c>
       <c r="S4" t="str">
-        <v>Rahul Kumar</v>
+        <v>Ishaan Desai</v>
       </c>
       <c r="T4">
-        <v>84162</v>
+        <v>43794</v>
       </c>
     </row>
     <row r="5">
@@ -652,22 +652,22 @@
         <v>REQ-2026-04</v>
       </c>
       <c r="B5" t="str">
-        <v>Sales</v>
+        <v>Technology</v>
       </c>
       <c r="C5" t="str">
-        <v>SMB</v>
+        <v>QA</v>
       </c>
       <c r="D5" t="str">
-        <v>Sales Executive</v>
+        <v>Senior SDE</v>
       </c>
       <c r="E5" t="str">
-        <v>L2</v>
+        <v>L6</v>
       </c>
       <c r="F5" t="str">
-        <v>Remote</v>
+        <v>Pune</v>
       </c>
       <c r="G5" t="str">
-        <v>Navya Khan</v>
+        <v>Karan Malhotra</v>
       </c>
       <c r="H5" t="str">
         <v>Contract</v>
@@ -676,37 +676,37 @@
         <v>Cancelled</v>
       </c>
       <c r="J5" t="str">
-        <v>2025-08-16</v>
+        <v>2025-09-19</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-07-22</v>
+        <v>2026-08-04</v>
       </c>
       <c r="L5">
-        <v>212</v>
+        <v>100</v>
       </c>
       <c r="M5">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="N5">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="O5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R5" t="str">
         <v>Agency</v>
       </c>
       <c r="S5" t="str">
-        <v>Farhan Joshi</v>
+        <v>Yash Desai</v>
       </c>
       <c r="T5">
-        <v>117903</v>
+        <v>23045</v>
       </c>
     </row>
     <row r="6">
@@ -717,58 +717,58 @@
         <v>Operations</v>
       </c>
       <c r="C6" t="str">
-        <v>Settlement</v>
+        <v>Risk</v>
       </c>
       <c r="D6" t="str">
-        <v>Ops Analyst</v>
+        <v>Ops Manager</v>
       </c>
       <c r="E6" t="str">
-        <v>L3</v>
+        <v>L4</v>
       </c>
       <c r="F6" t="str">
-        <v>Remote</v>
+        <v>Hyderabad</v>
       </c>
       <c r="G6" t="str">
-        <v>Vivaan Bose</v>
+        <v>Amit Singh</v>
       </c>
       <c r="H6" t="str">
         <v>FT</v>
       </c>
       <c r="I6" t="str">
-        <v>On-hold</v>
+        <v>Cancelled</v>
       </c>
       <c r="J6" t="str">
-        <v>2025-12-09</v>
+        <v>2025-12-07</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-05-21</v>
+        <v>2026-07-16</v>
       </c>
       <c r="L6">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="M6">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="O6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R6" t="str">
-        <v>Direct</v>
+        <v>Agency</v>
       </c>
       <c r="S6" t="str">
-        <v>Deepak Bhat</v>
+        <v>Aditya Verma</v>
       </c>
       <c r="T6">
-        <v>74054</v>
+        <v>99617</v>
       </c>
     </row>
     <row r="7">
@@ -776,49 +776,49 @@
         <v>REQ-2026-06</v>
       </c>
       <c r="B7" t="str">
-        <v>Human Resources</v>
+        <v>Sales</v>
       </c>
       <c r="C7" t="str">
-        <v>HR Operations &amp; Payroll</v>
+        <v>Inside Sales</v>
       </c>
       <c r="D7" t="str">
-        <v>HR Executive</v>
+        <v>Sales Executive</v>
       </c>
       <c r="E7" t="str">
-        <v>L5</v>
+        <v>L2</v>
       </c>
       <c r="F7" t="str">
-        <v>Pune</v>
+        <v>Bengaluru</v>
       </c>
       <c r="G7" t="str">
-        <v>Pari Kulkarni</v>
+        <v>Deepak Menon</v>
       </c>
       <c r="H7" t="str">
         <v>FT</v>
       </c>
       <c r="I7" t="str">
-        <v>Filled</v>
+        <v>Open</v>
       </c>
       <c r="J7" t="str">
-        <v>2025-12-09</v>
+        <v>2025-12-07</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-05-07</v>
+        <v>2026-06-15</v>
       </c>
       <c r="L7">
-        <v>102</v>
+        <v>164</v>
       </c>
       <c r="M7">
+        <v>31</v>
+      </c>
+      <c r="N7">
         <v>15</v>
       </c>
-      <c r="N7">
-        <v>7</v>
-      </c>
       <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="P7">
         <v>2</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -827,10 +827,10 @@
         <v>Portal</v>
       </c>
       <c r="S7" t="str">
-        <v>Aadhya Naidu</v>
+        <v>Nisha Bose</v>
       </c>
       <c r="T7">
-        <v>32948</v>
+        <v>39424</v>
       </c>
     </row>
     <row r="8">
@@ -838,61 +838,61 @@
         <v>REQ-2026-07</v>
       </c>
       <c r="B8" t="str">
-        <v>Sales</v>
+        <v>Marketing</v>
       </c>
       <c r="C8" t="str">
-        <v>Inside Sales</v>
+        <v>Digital</v>
       </c>
       <c r="D8" t="str">
-        <v>Account Manager</v>
+        <v>Marketing Manager</v>
       </c>
       <c r="E8" t="str">
-        <v>L2</v>
+        <v>L6</v>
       </c>
       <c r="F8" t="str">
-        <v>Remote</v>
+        <v>Pune</v>
       </c>
       <c r="G8" t="str">
-        <v>Saanvi Iyer</v>
+        <v>Karan Pillai</v>
       </c>
       <c r="H8" t="str">
         <v>FT</v>
       </c>
       <c r="I8" t="str">
-        <v>On-hold</v>
+        <v>Open</v>
       </c>
       <c r="J8" t="str">
-        <v>2025-12-25</v>
+        <v>2025-12-16</v>
       </c>
       <c r="K8" t="str">
-        <v>2026-07-11</v>
+        <v>2026-08-14</v>
       </c>
       <c r="L8">
-        <v>168</v>
+        <v>75</v>
       </c>
       <c r="M8">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="N8">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8" t="str">
-        <v>Direct</v>
+        <v>Referral</v>
       </c>
       <c r="S8" t="str">
-        <v>Arjun Shah</v>
+        <v>Vihaan Khan</v>
       </c>
       <c r="T8">
-        <v>114072</v>
+        <v>31220</v>
       </c>
     </row>
     <row r="9">
@@ -900,43 +900,43 @@
         <v>REQ-2026-08</v>
       </c>
       <c r="B9" t="str">
-        <v>Product</v>
+        <v>Technology</v>
       </c>
       <c r="C9" t="str">
-        <v>Core Product</v>
+        <v>Frontend</v>
       </c>
       <c r="D9" t="str">
-        <v>Senior PM</v>
+        <v>Tech Lead</v>
       </c>
       <c r="E9" t="str">
-        <v>L2</v>
+        <v>L4</v>
       </c>
       <c r="F9" t="str">
-        <v>Mumbai</v>
+        <v>Delhi</v>
       </c>
       <c r="G9" t="str">
-        <v>Imran Sheikh</v>
+        <v>Megha Naidu</v>
       </c>
       <c r="H9" t="str">
         <v>FT</v>
       </c>
       <c r="I9" t="str">
-        <v>Open</v>
+        <v>Cancelled</v>
       </c>
       <c r="J9" t="str">
-        <v>2025-12-20</v>
+        <v>2025-12-16</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-06-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="L9">
-        <v>124</v>
+        <v>190</v>
       </c>
       <c r="M9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N9">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O9">
         <v>5</v>
@@ -945,16 +945,16 @@
         <v>4</v>
       </c>
       <c r="Q9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R9" t="str">
-        <v>Internal</v>
+        <v>Agency</v>
       </c>
       <c r="S9" t="str">
-        <v>Sara Gupta</v>
+        <v>Rahul Bhat</v>
       </c>
       <c r="T9">
-        <v>83711</v>
+        <v>54039</v>
       </c>
     </row>
     <row r="10">
@@ -962,46 +962,46 @@
         <v>REQ-2026-09</v>
       </c>
       <c r="B10" t="str">
-        <v>Customer Support</v>
+        <v>Technology</v>
       </c>
       <c r="C10" t="str">
-        <v>L1 Support</v>
+        <v>DevOps</v>
       </c>
       <c r="D10" t="str">
-        <v>Support Associate</v>
+        <v>Engineering Manager</v>
       </c>
       <c r="E10" t="str">
-        <v>L5</v>
+        <v>L4</v>
       </c>
       <c r="F10" t="str">
-        <v>Bengaluru</v>
+        <v>Delhi</v>
       </c>
       <c r="G10" t="str">
-        <v>Vivaan Khan</v>
+        <v>Tara Menon</v>
       </c>
       <c r="H10" t="str">
-        <v>FT</v>
+        <v>Contract</v>
       </c>
       <c r="I10" t="str">
         <v>Filled</v>
       </c>
       <c r="J10" t="str">
-        <v>2025-12-09</v>
+        <v>2025-12-12</v>
       </c>
       <c r="K10" t="str">
-        <v>2026-08-22</v>
+        <v>2026-08-16</v>
       </c>
       <c r="L10">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="M10">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="N10">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="O10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <v>4</v>
@@ -1010,13 +1010,13 @@
         <v>4</v>
       </c>
       <c r="R10" t="str">
-        <v>Internal</v>
+        <v>Portal</v>
       </c>
       <c r="S10" t="str">
-        <v>Megha Das</v>
+        <v>Sneha Joshi</v>
       </c>
       <c r="T10">
-        <v>101696</v>
+        <v>82679</v>
       </c>
     </row>
     <row r="11">
@@ -1030,55 +1030,55 @@
         <v>L2 Support</v>
       </c>
       <c r="D11" t="str">
-        <v>Support Associate</v>
+        <v>Support Lead</v>
       </c>
       <c r="E11" t="str">
-        <v>L4</v>
+        <v>L3</v>
       </c>
       <c r="F11" t="str">
-        <v>Delhi</v>
+        <v>Pune</v>
       </c>
       <c r="G11" t="str">
-        <v>Sara Gupta</v>
+        <v>Pari Joshi</v>
       </c>
       <c r="H11" t="str">
-        <v>Intern</v>
+        <v>FT</v>
       </c>
       <c r="I11" t="str">
-        <v>Filled</v>
+        <v>Open</v>
       </c>
       <c r="J11" t="str">
-        <v>2025-12-17</v>
+        <v>2025-12-07</v>
       </c>
       <c r="K11" t="str">
-        <v>2026-08-17</v>
+        <v>2026-05-05</v>
       </c>
       <c r="L11">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="M11">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N11">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O11">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R11" t="str">
         <v>Referral</v>
       </c>
       <c r="S11" t="str">
-        <v>Imran Kulkarni</v>
+        <v>Aarohi Verma</v>
       </c>
       <c r="T11">
-        <v>80999</v>
+        <v>57744</v>
       </c>
     </row>
     <row r="12">
@@ -1086,61 +1086,61 @@
         <v>REQ-2026-11</v>
       </c>
       <c r="B12" t="str">
-        <v>Human Resources</v>
+        <v>Marketing</v>
       </c>
       <c r="C12" t="str">
-        <v>HR Operations &amp; Payroll</v>
+        <v>Digital</v>
       </c>
       <c r="D12" t="str">
-        <v>HRBP</v>
+        <v>Marketing Manager</v>
       </c>
       <c r="E12" t="str">
-        <v>L2</v>
+        <v>L4</v>
       </c>
       <c r="F12" t="str">
-        <v>Bengaluru</v>
+        <v>Mumbai</v>
       </c>
       <c r="G12" t="str">
-        <v>Nikhil Singh</v>
+        <v>Aarohi Iyer</v>
       </c>
       <c r="H12" t="str">
-        <v>Intern</v>
+        <v>FT</v>
       </c>
       <c r="I12" t="str">
-        <v>Open</v>
+        <v>On-hold</v>
       </c>
       <c r="J12" t="str">
-        <v>2025-12-15</v>
+        <v>2025-12-24</v>
       </c>
       <c r="K12" t="str">
-        <v>2026-07-11</v>
+        <v>2026-07-12</v>
       </c>
       <c r="L12">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="M12">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="N12">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="O12">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R12" t="str">
         <v>Referral</v>
       </c>
       <c r="S12" t="str">
-        <v>Rohan Menon</v>
+        <v>Saanvi Pillai</v>
       </c>
       <c r="T12">
-        <v>62742</v>
+        <v>28256</v>
       </c>
     </row>
     <row r="13">
@@ -1148,61 +1148,61 @@
         <v>REQ-2026-12</v>
       </c>
       <c r="B13" t="str">
-        <v>Human Resources</v>
+        <v>Product</v>
       </c>
       <c r="C13" t="str">
-        <v>Talent Acquisition</v>
+        <v>Growth</v>
       </c>
       <c r="D13" t="str">
-        <v>HR Executive</v>
+        <v>Product Manager</v>
       </c>
       <c r="E13" t="str">
-        <v>L3</v>
+        <v>L4</v>
       </c>
       <c r="F13" t="str">
-        <v>Delhi</v>
+        <v>Hyderabad</v>
       </c>
       <c r="G13" t="str">
-        <v>Arjun Sheikh</v>
+        <v>Anjali Verma</v>
       </c>
       <c r="H13" t="str">
         <v>FT</v>
       </c>
       <c r="I13" t="str">
-        <v>Filled</v>
+        <v>Open</v>
       </c>
       <c r="J13" t="str">
-        <v>2025-12-16</v>
+        <v>2025-12-28</v>
       </c>
       <c r="K13" t="str">
-        <v>2026-07-06</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L13">
-        <v>47</v>
+        <v>138</v>
       </c>
       <c r="M13">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="N13">
+        <v>16</v>
+      </c>
+      <c r="O13">
         <v>5</v>
       </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
       <c r="P13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R13" t="str">
-        <v>Portal</v>
+        <v>Agency</v>
       </c>
       <c r="S13" t="str">
-        <v>Kavya Sharma</v>
+        <v>Kabir Naidu</v>
       </c>
       <c r="T13">
-        <v>25836</v>
+        <v>104235</v>
       </c>
     </row>
     <row r="14">
@@ -1213,58 +1213,58 @@
         <v>Marketing</v>
       </c>
       <c r="C14" t="str">
-        <v>Brand</v>
+        <v>Digital</v>
       </c>
       <c r="D14" t="str">
         <v>Marketing Executive</v>
       </c>
       <c r="E14" t="str">
-        <v>L6</v>
+        <v>L2</v>
       </c>
       <c r="F14" t="str">
-        <v>Hyderabad</v>
+        <v>Mumbai</v>
       </c>
       <c r="G14" t="str">
-        <v>Tara Banerjee</v>
+        <v>Ananya Singh</v>
       </c>
       <c r="H14" t="str">
         <v>FT</v>
       </c>
       <c r="I14" t="str">
-        <v>On-hold</v>
+        <v>Filled</v>
       </c>
       <c r="J14" t="str">
-        <v>2025-12-11</v>
+        <v>2025-12-07</v>
       </c>
       <c r="K14" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-16</v>
       </c>
       <c r="L14">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="M14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="N14">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="O14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R14" t="str">
-        <v>Direct</v>
+        <v>Agency</v>
       </c>
       <c r="S14" t="str">
-        <v>Vikram Joshi</v>
+        <v>Anika Bose</v>
       </c>
       <c r="T14">
-        <v>32156</v>
+        <v>93809</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1275,19 @@
         <v>Technology</v>
       </c>
       <c r="C15" t="str">
-        <v>Frontend</v>
+        <v>QA</v>
       </c>
       <c r="D15" t="str">
-        <v>SDE II</v>
+        <v>Tech Lead</v>
       </c>
       <c r="E15" t="str">
         <v>L4</v>
       </c>
       <c r="F15" t="str">
-        <v>Hyderabad</v>
+        <v>Remote</v>
       </c>
       <c r="G15" t="str">
-        <v>Aarav Reddy</v>
+        <v>Farhan Desai</v>
       </c>
       <c r="H15" t="str">
         <v>FT</v>
@@ -1296,37 +1296,37 @@
         <v>Open</v>
       </c>
       <c r="J15" t="str">
-        <v>2025-12-11</v>
+        <v>2025-12-04</v>
       </c>
       <c r="K15" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-28</v>
       </c>
       <c r="L15">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="M15">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="N15">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="O15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R15" t="str">
         <v>Portal</v>
       </c>
       <c r="S15" t="str">
-        <v>Rohan Shah</v>
+        <v>Ira Mukherjee</v>
       </c>
       <c r="T15">
-        <v>92061</v>
+        <v>57439</v>
       </c>
     </row>
     <row r="16">
@@ -1334,61 +1334,61 @@
         <v>REQ-2026-15</v>
       </c>
       <c r="B16" t="str">
-        <v>Product</v>
+        <v>Technology</v>
       </c>
       <c r="C16" t="str">
-        <v>Growth</v>
+        <v>Backend</v>
       </c>
       <c r="D16" t="str">
-        <v>Product Manager</v>
+        <v>Tech Lead</v>
       </c>
       <c r="E16" t="str">
-        <v>L6</v>
+        <v>L2</v>
       </c>
       <c r="F16" t="str">
-        <v>Remote</v>
+        <v>Delhi</v>
       </c>
       <c r="G16" t="str">
-        <v>Sara Patel</v>
+        <v>Aadhya Bhat</v>
       </c>
       <c r="H16" t="str">
-        <v>FT</v>
+        <v>Intern</v>
       </c>
       <c r="I16" t="str">
-        <v>Filled</v>
+        <v>Open</v>
       </c>
       <c r="J16" t="str">
-        <v>2025-12-21</v>
+        <v>2025-12-09</v>
       </c>
       <c r="K16" t="str">
-        <v>2026-08-24</v>
+        <v>2026-08-26</v>
       </c>
       <c r="L16">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="M16">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="N16">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O16">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R16" t="str">
-        <v>Referral</v>
+        <v>Portal</v>
       </c>
       <c r="S16" t="str">
-        <v>Arjun Naidu</v>
+        <v>Aadhya Mehta</v>
       </c>
       <c r="T16">
-        <v>95494</v>
+        <v>109395</v>
       </c>
     </row>
     <row r="17">
@@ -1396,61 +1396,61 @@
         <v>REQ-2026-16</v>
       </c>
       <c r="B17" t="str">
-        <v>Technology</v>
+        <v>Operations</v>
       </c>
       <c r="C17" t="str">
-        <v>Data</v>
+        <v>Settlement</v>
       </c>
       <c r="D17" t="str">
-        <v>Engineering Manager</v>
+        <v>Ops Analyst</v>
       </c>
       <c r="E17" t="str">
-        <v>L4</v>
+        <v>L3</v>
       </c>
       <c r="F17" t="str">
-        <v>Pune</v>
+        <v>Bengaluru</v>
       </c>
       <c r="G17" t="str">
-        <v>Aadhya Lopes</v>
+        <v>Tara Singh</v>
       </c>
       <c r="H17" t="str">
         <v>FT</v>
       </c>
       <c r="I17" t="str">
-        <v>Filled</v>
+        <v>Open</v>
       </c>
       <c r="J17" t="str">
-        <v>2025-12-04</v>
+        <v>2025-12-05</v>
       </c>
       <c r="K17" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L17">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="M17">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O17">
         <v>2</v>
       </c>
       <c r="P17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R17" t="str">
-        <v>Referral</v>
+        <v>Agency</v>
       </c>
       <c r="S17" t="str">
-        <v>Aadhya Nair</v>
+        <v>Meera Malhotra</v>
       </c>
       <c r="T17">
-        <v>119879</v>
+        <v>34830</v>
       </c>
     </row>
     <row r="18">
@@ -1458,61 +1458,61 @@
         <v>REQ-2026-17</v>
       </c>
       <c r="B18" t="str">
-        <v>Customer Support</v>
+        <v>Marketing</v>
       </c>
       <c r="C18" t="str">
-        <v>L1 Support</v>
+        <v>Digital</v>
       </c>
       <c r="D18" t="str">
-        <v>Support Associate</v>
+        <v>Marketing Manager</v>
       </c>
       <c r="E18" t="str">
-        <v>L3</v>
+        <v>L2</v>
       </c>
       <c r="F18" t="str">
-        <v>Pune</v>
+        <v>Mumbai</v>
       </c>
       <c r="G18" t="str">
-        <v>Meera Malhotra</v>
+        <v>Ritu Fernandes</v>
       </c>
       <c r="H18" t="str">
         <v>FT</v>
       </c>
       <c r="I18" t="str">
-        <v>Filled</v>
+        <v>On-hold</v>
       </c>
       <c r="J18" t="str">
-        <v>2025-12-28</v>
+        <v>2025-12-01</v>
       </c>
       <c r="K18" t="str">
-        <v>2026-06-18</v>
+        <v>2026-06-27</v>
       </c>
       <c r="L18">
-        <v>97</v>
+        <v>154</v>
       </c>
       <c r="M18">
+        <v>32</v>
+      </c>
+      <c r="N18">
         <v>20</v>
       </c>
-      <c r="N18">
-        <v>10</v>
-      </c>
       <c r="O18">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R18" t="str">
-        <v>Agency</v>
+        <v>Direct</v>
       </c>
       <c r="S18" t="str">
-        <v>Deepak Desai</v>
+        <v>Kabir Mehta</v>
       </c>
       <c r="T18">
-        <v>110022</v>
+        <v>79449</v>
       </c>
     </row>
     <row r="19">
@@ -1532,49 +1532,49 @@
         <v>L6</v>
       </c>
       <c r="F19" t="str">
-        <v>Remote</v>
+        <v>Pune</v>
       </c>
       <c r="G19" t="str">
-        <v>Kabir Mehta</v>
+        <v>Myra Iyer</v>
       </c>
       <c r="H19" t="str">
         <v>FT</v>
       </c>
       <c r="I19" t="str">
-        <v>Cancelled</v>
+        <v>Open</v>
       </c>
       <c r="J19" t="str">
-        <v>2025-12-17</v>
+        <v>2025-12-16</v>
       </c>
       <c r="K19" t="str">
-        <v>2026-05-22</v>
+        <v>2026-08-08</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="M19">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="N19">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="O19">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R19" t="str">
-        <v>Portal</v>
+        <v>Internal</v>
       </c>
       <c r="S19" t="str">
-        <v>Sara Mukherjee</v>
+        <v>Kavya Iyer</v>
       </c>
       <c r="T19">
-        <v>53864</v>
+        <v>64850</v>
       </c>
     </row>
     <row r="20">
@@ -1582,61 +1582,61 @@
         <v>REQ-2026-19</v>
       </c>
       <c r="B20" t="str">
-        <v>Customer Support</v>
+        <v>Human Resources</v>
       </c>
       <c r="C20" t="str">
-        <v>L2 Support</v>
+        <v>HR Operations &amp; Payroll</v>
       </c>
       <c r="D20" t="str">
-        <v>Support Lead</v>
+        <v>Recruiter</v>
       </c>
       <c r="E20" t="str">
-        <v>L3</v>
+        <v>L2</v>
       </c>
       <c r="F20" t="str">
-        <v>Hyderabad</v>
+        <v>Mumbai</v>
       </c>
       <c r="G20" t="str">
-        <v>Kavya Iyer</v>
+        <v>Imran Nair</v>
       </c>
       <c r="H20" t="str">
         <v>FT</v>
       </c>
       <c r="I20" t="str">
-        <v>Open</v>
+        <v>Cancelled</v>
       </c>
       <c r="J20" t="str">
-        <v>2025-12-18</v>
+        <v>2025-12-20</v>
       </c>
       <c r="K20" t="str">
-        <v>2026-08-22</v>
+        <v>2026-07-21</v>
       </c>
       <c r="L20">
-        <v>49</v>
+        <v>178</v>
       </c>
       <c r="M20">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="N20">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="O20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R20" t="str">
         <v>Referral</v>
       </c>
       <c r="S20" t="str">
-        <v>Kavya Rao</v>
+        <v>Farhan Chopra</v>
       </c>
       <c r="T20">
-        <v>76659</v>
+        <v>68830</v>
       </c>
     </row>
     <row r="21">
@@ -1644,61 +1644,61 @@
         <v>REQ-2026-20</v>
       </c>
       <c r="B21" t="str">
-        <v>Finance</v>
+        <v>Human Resources</v>
       </c>
       <c r="C21" t="str">
-        <v>Accounts</v>
+        <v>Academy</v>
       </c>
       <c r="D21" t="str">
-        <v>Finance Manager</v>
+        <v>HRBP</v>
       </c>
       <c r="E21" t="str">
-        <v>L5</v>
+        <v>L2</v>
       </c>
       <c r="F21" t="str">
-        <v>Hyderabad</v>
+        <v>Bengaluru</v>
       </c>
       <c r="G21" t="str">
-        <v>Aarav Khan</v>
+        <v>Anika Sharma</v>
       </c>
       <c r="H21" t="str">
-        <v>FT</v>
+        <v>Intern</v>
       </c>
       <c r="I21" t="str">
         <v>Filled</v>
       </c>
       <c r="J21" t="str">
-        <v>2025-12-14</v>
+        <v>2025-12-05</v>
       </c>
       <c r="K21" t="str">
-        <v>2026-07-16</v>
+        <v>2026-07-18</v>
       </c>
       <c r="L21">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="M21">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="O21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R21" t="str">
-        <v>Agency</v>
+        <v>Direct</v>
       </c>
       <c r="S21" t="str">
-        <v>Pooja Desai</v>
+        <v>Ishaan Joshi</v>
       </c>
       <c r="T21">
-        <v>70695</v>
+        <v>82104</v>
       </c>
     </row>
     <row r="22">
@@ -1706,43 +1706,43 @@
         <v>REQ-2026-21</v>
       </c>
       <c r="B22" t="str">
-        <v>Customer Support</v>
+        <v>Product</v>
       </c>
       <c r="C22" t="str">
-        <v>L1 Support</v>
+        <v>Core Product</v>
       </c>
       <c r="D22" t="str">
-        <v>Support Lead</v>
+        <v>Product Manager</v>
       </c>
       <c r="E22" t="str">
-        <v>L5</v>
+        <v>L2</v>
       </c>
       <c r="F22" t="str">
-        <v>Remote</v>
+        <v>Mumbai</v>
       </c>
       <c r="G22" t="str">
-        <v>Ishaan Joshi</v>
+        <v>Deepak Desai</v>
       </c>
       <c r="H22" t="str">
-        <v>Contract</v>
+        <v>FT</v>
       </c>
       <c r="I22" t="str">
         <v>Cancelled</v>
       </c>
       <c r="J22" t="str">
-        <v>2025-12-22</v>
+        <v>2025-12-14</v>
       </c>
       <c r="K22" t="str">
-        <v>2026-08-13</v>
+        <v>2026-08-08</v>
       </c>
       <c r="L22">
-        <v>161</v>
+        <v>121</v>
       </c>
       <c r="M22">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N22">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O22">
         <v>4</v>
@@ -1757,10 +1757,10 @@
         <v>Portal</v>
       </c>
       <c r="S22" t="str">
-        <v>Priya Mehta</v>
+        <v>Krishna Banerjee</v>
       </c>
       <c r="T22">
-        <v>107375</v>
+        <v>88733</v>
       </c>
     </row>
     <row r="23">
@@ -1768,61 +1768,61 @@
         <v>REQ-2026-22</v>
       </c>
       <c r="B23" t="str">
-        <v>Operations</v>
+        <v>Finance</v>
       </c>
       <c r="C23" t="str">
-        <v>Merchant Ops</v>
+        <v>Accounts</v>
       </c>
       <c r="D23" t="str">
-        <v>Ops Executive</v>
+        <v>Finance Analyst</v>
       </c>
       <c r="E23" t="str">
-        <v>L5</v>
+        <v>L6</v>
       </c>
       <c r="F23" t="str">
         <v>Pune</v>
       </c>
       <c r="G23" t="str">
-        <v>Vikram Nair</v>
+        <v>Sara Joshi</v>
       </c>
       <c r="H23" t="str">
-        <v>Intern</v>
+        <v>FT</v>
       </c>
       <c r="I23" t="str">
-        <v>Filled</v>
+        <v>Cancelled</v>
       </c>
       <c r="J23" t="str">
-        <v>2025-12-20</v>
+        <v>2025-12-14</v>
       </c>
       <c r="K23" t="str">
-        <v>2026-07-26</v>
+        <v>2026-08-03</v>
       </c>
       <c r="L23">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="M23">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="N23">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="O23">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R23" t="str">
-        <v>Internal</v>
+        <v>Referral</v>
       </c>
       <c r="S23" t="str">
-        <v>Nisha Naidu</v>
+        <v>Sneha Patel</v>
       </c>
       <c r="T23">
-        <v>101688</v>
+        <v>47673</v>
       </c>
     </row>
     <row r="24">
@@ -1830,61 +1830,61 @@
         <v>REQ-2026-23</v>
       </c>
       <c r="B24" t="str">
-        <v>Marketing</v>
+        <v>Product</v>
       </c>
       <c r="C24" t="str">
-        <v>Digital</v>
+        <v>Growth</v>
       </c>
       <c r="D24" t="str">
-        <v>Marketing Executive</v>
+        <v>Senior PM</v>
       </c>
       <c r="E24" t="str">
-        <v>L6</v>
+        <v>L5</v>
       </c>
       <c r="F24" t="str">
-        <v>Mumbai</v>
+        <v>Hyderabad</v>
       </c>
       <c r="G24" t="str">
-        <v>Rohan Chopra</v>
+        <v>Priya Patel</v>
       </c>
       <c r="H24" t="str">
         <v>FT</v>
       </c>
       <c r="I24" t="str">
-        <v>Open</v>
+        <v>On-hold</v>
       </c>
       <c r="J24" t="str">
-        <v>2025-12-08</v>
+        <v>2025-12-13</v>
       </c>
       <c r="K24" t="str">
-        <v>2026-08-10</v>
+        <v>2026-05-05</v>
       </c>
       <c r="L24">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="M24">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="N24">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P24">
         <v>3</v>
       </c>
       <c r="Q24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R24" t="str">
         <v>Portal</v>
       </c>
       <c r="S24" t="str">
-        <v>Nisha Singh</v>
+        <v>Krishna Khan</v>
       </c>
       <c r="T24">
-        <v>54257</v>
+        <v>29577</v>
       </c>
     </row>
     <row r="25">
@@ -1892,22 +1892,22 @@
         <v>REQ-2026-24</v>
       </c>
       <c r="B25" t="str">
-        <v>Human Resources</v>
+        <v>Product</v>
       </c>
       <c r="C25" t="str">
-        <v>HR Operations &amp; Payroll</v>
+        <v>Growth</v>
       </c>
       <c r="D25" t="str">
-        <v>HRBP</v>
+        <v>Product Manager</v>
       </c>
       <c r="E25" t="str">
         <v>L4</v>
       </c>
       <c r="F25" t="str">
-        <v>Mumbai</v>
+        <v>Bengaluru</v>
       </c>
       <c r="G25" t="str">
-        <v>Krishna Chopra</v>
+        <v>Vihaan Mukherjee</v>
       </c>
       <c r="H25" t="str">
         <v>FT</v>
@@ -1916,37 +1916,37 @@
         <v>Filled</v>
       </c>
       <c r="J25" t="str">
-        <v>2025-12-23</v>
+        <v>2025-12-08</v>
       </c>
       <c r="K25" t="str">
         <v>2026-05-24</v>
       </c>
       <c r="L25">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="M25">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="N25">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R25" t="str">
-        <v>Direct</v>
+        <v>Internal</v>
       </c>
       <c r="S25" t="str">
-        <v>Aarav Kumar</v>
+        <v>Reyansh Kulkarni</v>
       </c>
       <c r="T25">
-        <v>54071</v>
+        <v>76334</v>
       </c>
     </row>
     <row r="26">
@@ -1960,55 +1960,55 @@
         <v>Accounts</v>
       </c>
       <c r="D26" t="str">
-        <v>Accountant</v>
+        <v>Finance Analyst</v>
       </c>
       <c r="E26" t="str">
         <v>L2</v>
       </c>
       <c r="F26" t="str">
-        <v>Remote</v>
+        <v>Bengaluru</v>
       </c>
       <c r="G26" t="str">
-        <v>Kavya Reddy</v>
+        <v>Ishaan Rao</v>
       </c>
       <c r="H26" t="str">
-        <v>Contract</v>
+        <v>FT</v>
       </c>
       <c r="I26" t="str">
-        <v>On-hold</v>
+        <v>Filled</v>
       </c>
       <c r="J26" t="str">
-        <v>2025-12-16</v>
+        <v>2025-12-24</v>
       </c>
       <c r="K26" t="str">
-        <v>2026-07-23</v>
+        <v>2026-06-22</v>
       </c>
       <c r="L26">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="M26">
         <v>32</v>
       </c>
       <c r="N26">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="O26">
         <v>5</v>
       </c>
       <c r="P26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R26" t="str">
-        <v>Internal</v>
+        <v>Portal</v>
       </c>
       <c r="S26" t="str">
-        <v>Ananya Mukherjee</v>
+        <v>Ritu Dsouza</v>
       </c>
       <c r="T26">
-        <v>29533</v>
+        <v>65123</v>
       </c>
     </row>
     <row r="27">
@@ -2016,61 +2016,61 @@
         <v>REQ-2026-26</v>
       </c>
       <c r="B27" t="str">
-        <v>Product</v>
+        <v>Finance</v>
       </c>
       <c r="C27" t="str">
-        <v>Growth</v>
+        <v>FP&amp;A</v>
       </c>
       <c r="D27" t="str">
-        <v>Product Manager</v>
+        <v>Accountant</v>
       </c>
       <c r="E27" t="str">
-        <v>L5</v>
+        <v>L3</v>
       </c>
       <c r="F27" t="str">
         <v>Bengaluru</v>
       </c>
       <c r="G27" t="str">
-        <v>Ritu Dsouza</v>
+        <v>Arjun Singh</v>
       </c>
       <c r="H27" t="str">
-        <v>FT</v>
+        <v>Contract</v>
       </c>
       <c r="I27" t="str">
         <v>Open</v>
       </c>
       <c r="J27" t="str">
-        <v>2025-12-17</v>
+        <v>2025-12-05</v>
       </c>
       <c r="K27" t="str">
-        <v>2026-05-25</v>
+        <v>2026-07-04</v>
       </c>
       <c r="L27">
-        <v>61</v>
+        <v>199</v>
       </c>
       <c r="M27">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="N27">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="O27">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R27" t="str">
-        <v>Internal</v>
+        <v>Direct</v>
       </c>
       <c r="S27" t="str">
-        <v>Aditya Bose</v>
+        <v>Farhan Das</v>
       </c>
       <c r="T27">
-        <v>61216</v>
+        <v>34871</v>
       </c>
     </row>
   </sheetData>
